--- a/public/demo/acme-sample-workbook.xlsx
+++ b/public/demo/acme-sample-workbook.xlsx
@@ -21560,7 +21560,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AO12"/>
+  <dimension ref="A1:AO11"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -22857,264 +22857,139 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Net Working Capital</v>
+        <v>Net Working Capital (Operating)</v>
       </c>
       <c r="B11" s="1">
-        <v>2040548</v>
+        <v>610473</v>
       </c>
       <c r="C11" s="1">
-        <v>3451980</v>
+        <v>663711</v>
       </c>
       <c r="D11" s="1">
-        <v>5036526</v>
+        <v>716948</v>
       </c>
       <c r="E11" s="1">
-        <v>5036526</v>
+        <v>716948</v>
       </c>
       <c r="F11" s="1">
-        <v>919780</v>
+        <v>579880</v>
       </c>
       <c r="G11" s="1">
-        <v>993651</v>
+        <v>564584</v>
       </c>
       <c r="H11" s="1">
-        <v>1110857</v>
+        <v>584979</v>
       </c>
       <c r="I11" s="1">
-        <v>1214678</v>
+        <v>590078</v>
       </c>
       <c r="J11" s="1">
-        <v>1313400</v>
+        <v>590078</v>
       </c>
       <c r="K11" s="1">
-        <v>1418631</v>
+        <v>595176</v>
       </c>
       <c r="L11" s="1">
-        <v>1511755</v>
+        <v>590078</v>
       </c>
       <c r="M11" s="1">
-        <v>1602967</v>
+        <v>584979</v>
       </c>
       <c r="N11" s="1">
-        <v>1706788</v>
+        <v>590078</v>
       </c>
       <c r="O11" s="1">
-        <v>1819529</v>
+        <v>600275</v>
       </c>
       <c r="P11" s="1">
-        <v>1929083</v>
+        <v>605374</v>
       </c>
       <c r="Q11" s="1">
-        <v>2040548</v>
+        <v>610473</v>
       </c>
       <c r="R11" s="1">
-        <v>2169753</v>
+        <v>630670</v>
       </c>
       <c r="S11" s="1">
-        <v>2256049</v>
+        <v>614150</v>
       </c>
       <c r="T11" s="1">
-        <v>2389148</v>
+        <v>636177</v>
       </c>
       <c r="U11" s="1">
-        <v>2507791</v>
+        <v>641684</v>
       </c>
       <c r="V11" s="1">
-        <v>2620927</v>
+        <v>641684</v>
       </c>
       <c r="W11" s="1">
-        <v>2741134</v>
+        <v>647191</v>
       </c>
       <c r="X11" s="1">
-        <v>2848263</v>
+        <v>641684</v>
       </c>
       <c r="Y11" s="1">
-        <v>2953328</v>
+        <v>636177</v>
       </c>
       <c r="Z11" s="1">
-        <v>3071971</v>
+        <v>641684</v>
       </c>
       <c r="AA11" s="1">
-        <v>3200247</v>
+        <v>652697</v>
       </c>
       <c r="AB11" s="1">
-        <v>3325081</v>
+        <v>658204</v>
       </c>
       <c r="AC11" s="1">
-        <v>3451980</v>
+        <v>663711</v>
       </c>
       <c r="AD11" s="1">
-        <v>3592846</v>
+        <v>681461</v>
       </c>
       <c r="AE11" s="1">
-        <v>3691567</v>
+        <v>663717</v>
       </c>
       <c r="AF11" s="1">
-        <v>3840559</v>
+        <v>687376</v>
       </c>
       <c r="AG11" s="1">
-        <v>3974022</v>
+        <v>693290</v>
       </c>
       <c r="AH11" s="1">
-        <v>4101571</v>
+        <v>693290</v>
       </c>
       <c r="AI11" s="1">
-        <v>4236753</v>
+        <v>699205</v>
       </c>
       <c r="AJ11" s="1">
-        <v>4357887</v>
+        <v>693290</v>
       </c>
       <c r="AK11" s="1">
-        <v>4476806</v>
+        <v>687376</v>
       </c>
       <c r="AL11" s="1">
-        <v>4610269</v>
+        <v>693290</v>
       </c>
       <c r="AM11" s="1">
-        <v>4754081</v>
+        <v>705119</v>
       </c>
       <c r="AN11" s="1">
-        <v>4894196</v>
+        <v>711034</v>
       </c>
       <c r="AO11" s="1">
-        <v>5036526</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>NWC ex. Cash</v>
-      </c>
-      <c r="B12" s="1">
-        <v>610473</v>
-      </c>
-      <c r="C12" s="1">
-        <v>663711</v>
-      </c>
-      <c r="D12" s="1">
-        <v>716948</v>
-      </c>
-      <c r="E12" s="1">
-        <v>716948</v>
-      </c>
-      <c r="F12" s="1">
-        <v>579880</v>
-      </c>
-      <c r="G12" s="1">
-        <v>564584</v>
-      </c>
-      <c r="H12" s="1">
-        <v>584979</v>
-      </c>
-      <c r="I12" s="1">
-        <v>590078</v>
-      </c>
-      <c r="J12" s="1">
-        <v>590078</v>
-      </c>
-      <c r="K12" s="1">
-        <v>595176</v>
-      </c>
-      <c r="L12" s="1">
-        <v>590078</v>
-      </c>
-      <c r="M12" s="1">
-        <v>584979</v>
-      </c>
-      <c r="N12" s="1">
-        <v>590078</v>
-      </c>
-      <c r="O12" s="1">
-        <v>600275</v>
-      </c>
-      <c r="P12" s="1">
-        <v>605374</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>610473</v>
-      </c>
-      <c r="R12" s="1">
-        <v>630670</v>
-      </c>
-      <c r="S12" s="1">
-        <v>614150</v>
-      </c>
-      <c r="T12" s="1">
-        <v>636177</v>
-      </c>
-      <c r="U12" s="1">
-        <v>641684</v>
-      </c>
-      <c r="V12" s="1">
-        <v>641684</v>
-      </c>
-      <c r="W12" s="1">
-        <v>647191</v>
-      </c>
-      <c r="X12" s="1">
-        <v>641684</v>
-      </c>
-      <c r="Y12" s="1">
-        <v>636177</v>
-      </c>
-      <c r="Z12" s="1">
-        <v>641684</v>
-      </c>
-      <c r="AA12" s="1">
-        <v>652697</v>
-      </c>
-      <c r="AB12" s="1">
-        <v>658204</v>
-      </c>
-      <c r="AC12" s="1">
-        <v>663711</v>
-      </c>
-      <c r="AD12" s="1">
-        <v>681461</v>
-      </c>
-      <c r="AE12" s="1">
-        <v>663717</v>
-      </c>
-      <c r="AF12" s="1">
-        <v>687376</v>
-      </c>
-      <c r="AG12" s="1">
-        <v>693290</v>
-      </c>
-      <c r="AH12" s="1">
-        <v>693290</v>
-      </c>
-      <c r="AI12" s="1">
-        <v>699205</v>
-      </c>
-      <c r="AJ12" s="1">
-        <v>693290</v>
-      </c>
-      <c r="AK12" s="1">
-        <v>687376</v>
-      </c>
-      <c r="AL12" s="1">
-        <v>693290</v>
-      </c>
-      <c r="AM12" s="1">
-        <v>705119</v>
-      </c>
-      <c r="AN12" s="1">
-        <v>711034</v>
-      </c>
-      <c r="AO12" s="1">
         <v>716948</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AO12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AO11"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AO17"/>
+  <dimension ref="A1:AO16"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -23286,7 +23161,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Net working capital - reported to adjusted</v>
+        <v>Reported balance sheet</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -24286,7 +24161,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Net working capital</v>
+        <v>Net working capital, reported</v>
       </c>
       <c r="B10" s="1">
         <v>2040548</v>
@@ -24411,7 +24286,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Normal NWC adjustments</v>
+        <v>Bridge to Operating NWC</v>
       </c>
       <c r="B11" t="str">
         <v/>
@@ -24536,7 +24411,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v xml:space="preserve">  Remove: Cash and cash equivalents</v>
+        <v xml:space="preserve">  Less: Cash and cash equivalents</v>
       </c>
       <c r="B12" s="1">
         <v>-1430075</v>
@@ -24661,7 +24536,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Net working capital, reported (ex. cash)</v>
+        <v>Net working capital (Operating)</v>
       </c>
       <c r="B13" s="1">
         <v>610473</v>
@@ -24786,514 +24661,389 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Net working capital, adjusted</v>
-      </c>
-      <c r="B14" s="1">
-        <v>610473</v>
-      </c>
-      <c r="C14" s="1">
-        <v>663711</v>
-      </c>
-      <c r="D14" s="1">
-        <v>716948</v>
-      </c>
-      <c r="E14" s="1">
-        <v>716948</v>
-      </c>
-      <c r="F14" s="1">
-        <v>579880</v>
-      </c>
-      <c r="G14" s="1">
-        <v>564584</v>
-      </c>
-      <c r="H14" s="1">
-        <v>584979</v>
-      </c>
-      <c r="I14" s="1">
-        <v>590078</v>
-      </c>
-      <c r="J14" s="1">
-        <v>590078</v>
-      </c>
-      <c r="K14" s="1">
-        <v>595176</v>
-      </c>
-      <c r="L14" s="1">
-        <v>590078</v>
-      </c>
-      <c r="M14" s="1">
-        <v>584979</v>
-      </c>
-      <c r="N14" s="1">
-        <v>590078</v>
-      </c>
-      <c r="O14" s="1">
-        <v>600275</v>
-      </c>
-      <c r="P14" s="1">
-        <v>605374</v>
-      </c>
-      <c r="Q14" s="1">
-        <v>610473</v>
-      </c>
-      <c r="R14" s="1">
-        <v>630670</v>
-      </c>
-      <c r="S14" s="1">
-        <v>614150</v>
-      </c>
-      <c r="T14" s="1">
-        <v>636177</v>
-      </c>
-      <c r="U14" s="1">
-        <v>641684</v>
-      </c>
-      <c r="V14" s="1">
-        <v>641684</v>
-      </c>
-      <c r="W14" s="1">
-        <v>647191</v>
-      </c>
-      <c r="X14" s="1">
-        <v>641684</v>
-      </c>
-      <c r="Y14" s="1">
-        <v>636177</v>
-      </c>
-      <c r="Z14" s="1">
-        <v>641684</v>
-      </c>
-      <c r="AA14" s="1">
-        <v>652697</v>
-      </c>
-      <c r="AB14" s="1">
-        <v>658204</v>
-      </c>
-      <c r="AC14" s="1">
-        <v>663711</v>
-      </c>
-      <c r="AD14" s="1">
-        <v>681461</v>
-      </c>
-      <c r="AE14" s="1">
-        <v>663717</v>
-      </c>
-      <c r="AF14" s="1">
-        <v>687376</v>
-      </c>
-      <c r="AG14" s="1">
-        <v>693290</v>
-      </c>
-      <c r="AH14" s="1">
-        <v>693290</v>
-      </c>
-      <c r="AI14" s="1">
-        <v>699205</v>
-      </c>
-      <c r="AJ14" s="1">
-        <v>693290</v>
-      </c>
-      <c r="AK14" s="1">
-        <v>687376</v>
-      </c>
-      <c r="AL14" s="1">
-        <v>693290</v>
-      </c>
-      <c r="AM14" s="1">
-        <v>705119</v>
-      </c>
-      <c r="AN14" s="1">
-        <v>711034</v>
-      </c>
-      <c r="AO14" s="1">
-        <v>716948</v>
+        <v>Trailing Averages</v>
+      </c>
+      <c r="B14" t="str">
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+      <c r="Q14" t="str">
+        <v/>
+      </c>
+      <c r="R14" t="str">
+        <v/>
+      </c>
+      <c r="S14" t="str">
+        <v/>
+      </c>
+      <c r="T14" t="str">
+        <v/>
+      </c>
+      <c r="U14" t="str">
+        <v/>
+      </c>
+      <c r="V14" t="str">
+        <v/>
+      </c>
+      <c r="W14" t="str">
+        <v/>
+      </c>
+      <c r="X14" t="str">
+        <v/>
+      </c>
+      <c r="Y14" t="str">
+        <v/>
+      </c>
+      <c r="Z14" t="str">
+        <v/>
+      </c>
+      <c r="AA14" t="str">
+        <v/>
+      </c>
+      <c r="AB14" t="str">
+        <v/>
+      </c>
+      <c r="AC14" t="str">
+        <v/>
+      </c>
+      <c r="AD14" t="str">
+        <v/>
+      </c>
+      <c r="AE14" t="str">
+        <v/>
+      </c>
+      <c r="AF14" t="str">
+        <v/>
+      </c>
+      <c r="AG14" t="str">
+        <v/>
+      </c>
+      <c r="AH14" t="str">
+        <v/>
+      </c>
+      <c r="AI14" t="str">
+        <v/>
+      </c>
+      <c r="AJ14" t="str">
+        <v/>
+      </c>
+      <c r="AK14" t="str">
+        <v/>
+      </c>
+      <c r="AL14" t="str">
+        <v/>
+      </c>
+      <c r="AM14" t="str">
+        <v/>
+      </c>
+      <c r="AN14" t="str">
+        <v/>
+      </c>
+      <c r="AO14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Trailing Averages</v>
-      </c>
-      <c r="B15" t="str">
-        <v/>
-      </c>
-      <c r="C15" t="str">
-        <v/>
-      </c>
-      <c r="D15" t="str">
-        <v/>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v/>
-      </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str">
-        <v/>
-      </c>
-      <c r="M15" t="str">
-        <v/>
-      </c>
-      <c r="N15" t="str">
-        <v/>
-      </c>
-      <c r="O15" t="str">
-        <v/>
-      </c>
-      <c r="P15" t="str">
-        <v/>
-      </c>
-      <c r="Q15" t="str">
-        <v/>
-      </c>
-      <c r="R15" t="str">
-        <v/>
-      </c>
-      <c r="S15" t="str">
-        <v/>
-      </c>
-      <c r="T15" t="str">
-        <v/>
-      </c>
-      <c r="U15" t="str">
-        <v/>
-      </c>
-      <c r="V15" t="str">
-        <v/>
-      </c>
-      <c r="W15" t="str">
-        <v/>
-      </c>
-      <c r="X15" t="str">
-        <v/>
-      </c>
-      <c r="Y15" t="str">
-        <v/>
-      </c>
-      <c r="Z15" t="str">
-        <v/>
-      </c>
-      <c r="AA15" t="str">
-        <v/>
-      </c>
-      <c r="AB15" t="str">
-        <v/>
-      </c>
-      <c r="AC15" t="str">
-        <v/>
-      </c>
-      <c r="AD15" t="str">
-        <v/>
-      </c>
-      <c r="AE15" t="str">
-        <v/>
-      </c>
-      <c r="AF15" t="str">
-        <v/>
-      </c>
-      <c r="AG15" t="str">
-        <v/>
-      </c>
-      <c r="AH15" t="str">
-        <v/>
-      </c>
-      <c r="AI15" t="str">
-        <v/>
-      </c>
-      <c r="AJ15" t="str">
-        <v/>
-      </c>
-      <c r="AK15" t="str">
-        <v/>
-      </c>
-      <c r="AL15" t="str">
-        <v/>
-      </c>
-      <c r="AM15" t="str">
-        <v/>
-      </c>
-      <c r="AN15" t="str">
-        <v/>
-      </c>
-      <c r="AO15" t="str">
-        <v/>
+        <v>A/R Days Outstanding</v>
+      </c>
+      <c r="B15">
+        <v>47.466</v>
+      </c>
+      <c r="C15">
+        <v>47.325</v>
+      </c>
+      <c r="D15">
+        <v>47.204</v>
+      </c>
+      <c r="E15">
+        <v>47.204</v>
+      </c>
+      <c r="F15">
+        <v>47.547</v>
+      </c>
+      <c r="G15">
+        <v>47.592</v>
+      </c>
+      <c r="H15">
+        <v>47.533</v>
+      </c>
+      <c r="I15">
+        <v>47.519</v>
+      </c>
+      <c r="J15">
+        <v>47.519</v>
+      </c>
+      <c r="K15">
+        <v>47.505</v>
+      </c>
+      <c r="L15">
+        <v>47.519</v>
+      </c>
+      <c r="M15">
+        <v>47.533</v>
+      </c>
+      <c r="N15">
+        <v>47.519</v>
+      </c>
+      <c r="O15">
+        <v>47.492</v>
+      </c>
+      <c r="P15">
+        <v>47.479</v>
+      </c>
+      <c r="Q15">
+        <v>47.466</v>
+      </c>
+      <c r="R15">
+        <v>47.397</v>
+      </c>
+      <c r="S15">
+        <v>47.437</v>
+      </c>
+      <c r="T15">
+        <v>47.384</v>
+      </c>
+      <c r="U15">
+        <v>47.372</v>
+      </c>
+      <c r="V15">
+        <v>47.372</v>
+      </c>
+      <c r="W15">
+        <v>47.36</v>
+      </c>
+      <c r="X15">
+        <v>47.372</v>
+      </c>
+      <c r="Y15">
+        <v>47.384</v>
+      </c>
+      <c r="Z15">
+        <v>47.372</v>
+      </c>
+      <c r="AA15">
+        <v>47.348</v>
+      </c>
+      <c r="AB15">
+        <v>47.336</v>
+      </c>
+      <c r="AC15">
+        <v>47.325</v>
+      </c>
+      <c r="AD15">
+        <v>47.268</v>
+      </c>
+      <c r="AE15">
+        <v>47.304</v>
+      </c>
+      <c r="AF15">
+        <v>47.257</v>
+      </c>
+      <c r="AG15">
+        <v>47.246</v>
+      </c>
+      <c r="AH15">
+        <v>47.246</v>
+      </c>
+      <c r="AI15">
+        <v>47.235</v>
+      </c>
+      <c r="AJ15">
+        <v>47.246</v>
+      </c>
+      <c r="AK15">
+        <v>47.257</v>
+      </c>
+      <c r="AL15">
+        <v>47.246</v>
+      </c>
+      <c r="AM15">
+        <v>47.224</v>
+      </c>
+      <c r="AN15">
+        <v>47.214</v>
+      </c>
+      <c r="AO15">
+        <v>47.204</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>A/R Days Outstanding</v>
+        <v>A/P Days Outstanding</v>
       </c>
       <c r="B16">
-        <v>47.466</v>
+        <v>25.571</v>
       </c>
       <c r="C16">
-        <v>47.325</v>
+        <v>24.899</v>
       </c>
       <c r="D16">
-        <v>47.204</v>
+        <v>24.32</v>
       </c>
       <c r="E16">
-        <v>47.204</v>
+        <v>24.32</v>
       </c>
       <c r="F16">
-        <v>47.547</v>
+        <v>26.115</v>
       </c>
       <c r="G16">
-        <v>47.592</v>
+        <v>26.413</v>
       </c>
       <c r="H16">
-        <v>47.533</v>
+        <v>26.02</v>
       </c>
       <c r="I16">
-        <v>47.519</v>
+        <v>25.927</v>
       </c>
       <c r="J16">
-        <v>47.519</v>
+        <v>25.927</v>
       </c>
       <c r="K16">
-        <v>47.505</v>
+        <v>25.835</v>
       </c>
       <c r="L16">
-        <v>47.519</v>
+        <v>25.927</v>
       </c>
       <c r="M16">
-        <v>47.533</v>
+        <v>26.02</v>
       </c>
       <c r="N16">
-        <v>47.519</v>
+        <v>25.927</v>
       </c>
       <c r="O16">
-        <v>47.492</v>
+        <v>25.746</v>
       </c>
       <c r="P16">
-        <v>47.479</v>
+        <v>25.658</v>
       </c>
       <c r="Q16">
-        <v>47.466</v>
+        <v>25.571</v>
       </c>
       <c r="R16">
-        <v>47.397</v>
+        <v>25.403</v>
       </c>
       <c r="S16">
-        <v>47.437</v>
+        <v>25.679</v>
       </c>
       <c r="T16">
-        <v>47.384</v>
+        <v>25.315</v>
       </c>
       <c r="U16">
-        <v>47.372</v>
+        <v>25.229</v>
       </c>
       <c r="V16">
-        <v>47.372</v>
+        <v>25.229</v>
       </c>
       <c r="W16">
-        <v>47.36</v>
+        <v>25.144</v>
       </c>
       <c r="X16">
-        <v>47.372</v>
+        <v>25.229</v>
       </c>
       <c r="Y16">
-        <v>47.384</v>
+        <v>25.315</v>
       </c>
       <c r="Z16">
-        <v>47.372</v>
+        <v>25.229</v>
       </c>
       <c r="AA16">
-        <v>47.348</v>
+        <v>25.061</v>
       </c>
       <c r="AB16">
-        <v>47.336</v>
+        <v>24.979</v>
       </c>
       <c r="AC16">
-        <v>47.325</v>
+        <v>24.899</v>
       </c>
       <c r="AD16">
-        <v>47.268</v>
+        <v>24.789</v>
       </c>
       <c r="AE16">
-        <v>47.304</v>
+        <v>25.045</v>
       </c>
       <c r="AF16">
-        <v>47.257</v>
+        <v>24.707</v>
       </c>
       <c r="AG16">
-        <v>47.246</v>
+        <v>24.627</v>
       </c>
       <c r="AH16">
-        <v>47.246</v>
+        <v>24.627</v>
       </c>
       <c r="AI16">
-        <v>47.235</v>
+        <v>24.548</v>
       </c>
       <c r="AJ16">
-        <v>47.246</v>
+        <v>24.627</v>
       </c>
       <c r="AK16">
-        <v>47.257</v>
+        <v>24.707</v>
       </c>
       <c r="AL16">
-        <v>47.246</v>
+        <v>24.627</v>
       </c>
       <c r="AM16">
-        <v>47.224</v>
+        <v>24.47</v>
       </c>
       <c r="AN16">
-        <v>47.214</v>
+        <v>24.394</v>
       </c>
       <c r="AO16">
-        <v>47.204</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>A/P Days Outstanding</v>
-      </c>
-      <c r="B17">
-        <v>25.571</v>
-      </c>
-      <c r="C17">
-        <v>24.899</v>
-      </c>
-      <c r="D17">
-        <v>24.32</v>
-      </c>
-      <c r="E17">
-        <v>24.32</v>
-      </c>
-      <c r="F17">
-        <v>26.115</v>
-      </c>
-      <c r="G17">
-        <v>26.413</v>
-      </c>
-      <c r="H17">
-        <v>26.02</v>
-      </c>
-      <c r="I17">
-        <v>25.927</v>
-      </c>
-      <c r="J17">
-        <v>25.927</v>
-      </c>
-      <c r="K17">
-        <v>25.835</v>
-      </c>
-      <c r="L17">
-        <v>25.927</v>
-      </c>
-      <c r="M17">
-        <v>26.02</v>
-      </c>
-      <c r="N17">
-        <v>25.927</v>
-      </c>
-      <c r="O17">
-        <v>25.746</v>
-      </c>
-      <c r="P17">
-        <v>25.658</v>
-      </c>
-      <c r="Q17">
-        <v>25.571</v>
-      </c>
-      <c r="R17">
-        <v>25.403</v>
-      </c>
-      <c r="S17">
-        <v>25.679</v>
-      </c>
-      <c r="T17">
-        <v>25.315</v>
-      </c>
-      <c r="U17">
-        <v>25.229</v>
-      </c>
-      <c r="V17">
-        <v>25.229</v>
-      </c>
-      <c r="W17">
-        <v>25.144</v>
-      </c>
-      <c r="X17">
-        <v>25.229</v>
-      </c>
-      <c r="Y17">
-        <v>25.315</v>
-      </c>
-      <c r="Z17">
-        <v>25.229</v>
-      </c>
-      <c r="AA17">
-        <v>25.061</v>
-      </c>
-      <c r="AB17">
-        <v>24.979</v>
-      </c>
-      <c r="AC17">
-        <v>24.899</v>
-      </c>
-      <c r="AD17">
-        <v>24.789</v>
-      </c>
-      <c r="AE17">
-        <v>25.045</v>
-      </c>
-      <c r="AF17">
-        <v>24.707</v>
-      </c>
-      <c r="AG17">
-        <v>24.627</v>
-      </c>
-      <c r="AH17">
-        <v>24.627</v>
-      </c>
-      <c r="AI17">
-        <v>24.548</v>
-      </c>
-      <c r="AJ17">
-        <v>24.627</v>
-      </c>
-      <c r="AK17">
-        <v>24.707</v>
-      </c>
-      <c r="AL17">
-        <v>24.627</v>
-      </c>
-      <c r="AM17">
-        <v>24.47</v>
-      </c>
-      <c r="AN17">
-        <v>24.394</v>
-      </c>
-      <c r="AO17">
         <v>24.32</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AO17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AO16"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AO18"/>
+  <dimension ref="A1:AO21"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -26340,1257 +26090,1632 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>TOTAL ASSETS</v>
+        <v>Total Non-Current Assets</v>
       </c>
       <c r="B9" s="1">
-        <v>2941875</v>
+        <v>634000</v>
       </c>
       <c r="C9" s="1">
-        <v>4267493</v>
+        <v>538000</v>
       </c>
       <c r="D9" s="1">
-        <v>5766226</v>
+        <v>442000</v>
       </c>
       <c r="E9" s="1">
-        <v>5766226</v>
+        <v>442000</v>
       </c>
       <c r="F9" s="1">
-        <v>1901900</v>
+        <v>722000</v>
       </c>
       <c r="G9" s="1">
-        <v>1964167</v>
+        <v>714000</v>
       </c>
       <c r="H9" s="1">
-        <v>2078178</v>
+        <v>706000</v>
       </c>
       <c r="I9" s="1">
-        <v>2175200</v>
+        <v>698000</v>
       </c>
       <c r="J9" s="1">
-        <v>2265922</v>
+        <v>690000</v>
       </c>
       <c r="K9" s="1">
-        <v>2364355</v>
+        <v>682000</v>
       </c>
       <c r="L9" s="1">
-        <v>2448277</v>
+        <v>674000</v>
       </c>
       <c r="M9" s="1">
-        <v>2530288</v>
+        <v>666000</v>
       </c>
       <c r="N9" s="1">
-        <v>2627310</v>
+        <v>658000</v>
       </c>
       <c r="O9" s="1">
-        <v>2734454</v>
+        <v>650000</v>
       </c>
       <c r="P9" s="1">
-        <v>2837209</v>
+        <v>642000</v>
       </c>
       <c r="Q9" s="1">
-        <v>2941875</v>
+        <v>634000</v>
       </c>
       <c r="R9" s="1">
-        <v>3065483</v>
+        <v>626000</v>
       </c>
       <c r="S9" s="1">
-        <v>3139887</v>
+        <v>618000</v>
       </c>
       <c r="T9" s="1">
-        <v>3270175</v>
+        <v>610000</v>
       </c>
       <c r="U9" s="1">
-        <v>3382115</v>
+        <v>602000</v>
       </c>
       <c r="V9" s="1">
-        <v>3487251</v>
+        <v>594000</v>
       </c>
       <c r="W9" s="1">
-        <v>3600755</v>
+        <v>586000</v>
       </c>
       <c r="X9" s="1">
-        <v>3698587</v>
+        <v>578000</v>
       </c>
       <c r="Y9" s="1">
-        <v>3794355</v>
+        <v>570000</v>
       </c>
       <c r="Z9" s="1">
-        <v>3906295</v>
+        <v>562000</v>
       </c>
       <c r="AA9" s="1">
-        <v>4029166</v>
+        <v>554000</v>
       </c>
       <c r="AB9" s="1">
-        <v>4147297</v>
+        <v>546000</v>
       </c>
       <c r="AC9" s="1">
-        <v>4267493</v>
+        <v>538000</v>
       </c>
       <c r="AD9" s="1">
-        <v>4402185</v>
+        <v>530000</v>
       </c>
       <c r="AE9" s="1">
-        <v>4488726</v>
+        <v>522000</v>
       </c>
       <c r="AF9" s="1">
-        <v>4635291</v>
+        <v>514000</v>
       </c>
       <c r="AG9" s="1">
-        <v>4762148</v>
+        <v>506000</v>
       </c>
       <c r="AH9" s="1">
-        <v>4881697</v>
+        <v>498000</v>
       </c>
       <c r="AI9" s="1">
-        <v>5010272</v>
+        <v>490000</v>
       </c>
       <c r="AJ9" s="1">
-        <v>5122013</v>
+        <v>482000</v>
       </c>
       <c r="AK9" s="1">
-        <v>5231538</v>
+        <v>474000</v>
       </c>
       <c r="AL9" s="1">
-        <v>5358395</v>
+        <v>466000</v>
       </c>
       <c r="AM9" s="1">
-        <v>5496994</v>
+        <v>458000</v>
       </c>
       <c r="AN9" s="1">
-        <v>5630502</v>
+        <v>450000</v>
       </c>
       <c r="AO9" s="1">
-        <v>5766226</v>
+        <v>442000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>LIABILITIES</v>
-      </c>
-      <c r="B10" t="str">
-        <v/>
-      </c>
-      <c r="C10" t="str">
-        <v/>
-      </c>
-      <c r="D10" t="str">
-        <v/>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v/>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v/>
-      </c>
-      <c r="M10" t="str">
-        <v/>
-      </c>
-      <c r="N10" t="str">
-        <v/>
-      </c>
-      <c r="O10" t="str">
-        <v/>
-      </c>
-      <c r="P10" t="str">
-        <v/>
-      </c>
-      <c r="Q10" t="str">
-        <v/>
-      </c>
-      <c r="R10" t="str">
-        <v/>
-      </c>
-      <c r="S10" t="str">
-        <v/>
-      </c>
-      <c r="T10" t="str">
-        <v/>
-      </c>
-      <c r="U10" t="str">
-        <v/>
-      </c>
-      <c r="V10" t="str">
-        <v/>
-      </c>
-      <c r="W10" t="str">
-        <v/>
-      </c>
-      <c r="X10" t="str">
-        <v/>
-      </c>
-      <c r="Y10" t="str">
-        <v/>
-      </c>
-      <c r="Z10" t="str">
-        <v/>
-      </c>
-      <c r="AA10" t="str">
-        <v/>
-      </c>
-      <c r="AB10" t="str">
-        <v/>
-      </c>
-      <c r="AC10" t="str">
-        <v/>
-      </c>
-      <c r="AD10" t="str">
-        <v/>
-      </c>
-      <c r="AE10" t="str">
-        <v/>
-      </c>
-      <c r="AF10" t="str">
-        <v/>
-      </c>
-      <c r="AG10" t="str">
-        <v/>
-      </c>
-      <c r="AH10" t="str">
-        <v/>
-      </c>
-      <c r="AI10" t="str">
-        <v/>
-      </c>
-      <c r="AJ10" t="str">
-        <v/>
-      </c>
-      <c r="AK10" t="str">
-        <v/>
-      </c>
-      <c r="AL10" t="str">
-        <v/>
-      </c>
-      <c r="AM10" t="str">
-        <v/>
-      </c>
-      <c r="AN10" t="str">
-        <v/>
-      </c>
-      <c r="AO10" t="str">
-        <v/>
+        <v>TOTAL ASSETS</v>
+      </c>
+      <c r="B10" s="1">
+        <v>2941875</v>
+      </c>
+      <c r="C10" s="1">
+        <v>4267493</v>
+      </c>
+      <c r="D10" s="1">
+        <v>5766226</v>
+      </c>
+      <c r="E10" s="1">
+        <v>5766226</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1901900</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1964167</v>
+      </c>
+      <c r="H10" s="1">
+        <v>2078178</v>
+      </c>
+      <c r="I10" s="1">
+        <v>2175200</v>
+      </c>
+      <c r="J10" s="1">
+        <v>2265922</v>
+      </c>
+      <c r="K10" s="1">
+        <v>2364355</v>
+      </c>
+      <c r="L10" s="1">
+        <v>2448277</v>
+      </c>
+      <c r="M10" s="1">
+        <v>2530288</v>
+      </c>
+      <c r="N10" s="1">
+        <v>2627310</v>
+      </c>
+      <c r="O10" s="1">
+        <v>2734454</v>
+      </c>
+      <c r="P10" s="1">
+        <v>2837209</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>2941875</v>
+      </c>
+      <c r="R10" s="1">
+        <v>3065483</v>
+      </c>
+      <c r="S10" s="1">
+        <v>3139887</v>
+      </c>
+      <c r="T10" s="1">
+        <v>3270175</v>
+      </c>
+      <c r="U10" s="1">
+        <v>3382115</v>
+      </c>
+      <c r="V10" s="1">
+        <v>3487251</v>
+      </c>
+      <c r="W10" s="1">
+        <v>3600755</v>
+      </c>
+      <c r="X10" s="1">
+        <v>3698587</v>
+      </c>
+      <c r="Y10" s="1">
+        <v>3794355</v>
+      </c>
+      <c r="Z10" s="1">
+        <v>3906295</v>
+      </c>
+      <c r="AA10" s="1">
+        <v>4029166</v>
+      </c>
+      <c r="AB10" s="1">
+        <v>4147297</v>
+      </c>
+      <c r="AC10" s="1">
+        <v>4267493</v>
+      </c>
+      <c r="AD10" s="1">
+        <v>4402185</v>
+      </c>
+      <c r="AE10" s="1">
+        <v>4488726</v>
+      </c>
+      <c r="AF10" s="1">
+        <v>4635291</v>
+      </c>
+      <c r="AG10" s="1">
+        <v>4762148</v>
+      </c>
+      <c r="AH10" s="1">
+        <v>4881697</v>
+      </c>
+      <c r="AI10" s="1">
+        <v>5010272</v>
+      </c>
+      <c r="AJ10" s="1">
+        <v>5122013</v>
+      </c>
+      <c r="AK10" s="1">
+        <v>5231538</v>
+      </c>
+      <c r="AL10" s="1">
+        <v>5358395</v>
+      </c>
+      <c r="AM10" s="1">
+        <v>5496994</v>
+      </c>
+      <c r="AN10" s="1">
+        <v>5630502</v>
+      </c>
+      <c r="AO10" s="1">
+        <v>5766226</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v xml:space="preserve">  Current Liabilities</v>
-      </c>
-      <c r="B11" s="1">
-        <v>197327</v>
-      </c>
-      <c r="C11" s="1">
-        <v>207513</v>
-      </c>
-      <c r="D11" s="1">
-        <v>217700</v>
-      </c>
-      <c r="E11" s="1">
-        <v>217700</v>
-      </c>
-      <c r="F11" s="1">
-        <v>190120</v>
-      </c>
-      <c r="G11" s="1">
-        <v>186516</v>
-      </c>
-      <c r="H11" s="1">
-        <v>191321</v>
-      </c>
-      <c r="I11" s="1">
-        <v>192522</v>
-      </c>
-      <c r="J11" s="1">
-        <v>192522</v>
-      </c>
-      <c r="K11" s="1">
-        <v>193724</v>
-      </c>
-      <c r="L11" s="1">
-        <v>192522</v>
-      </c>
-      <c r="M11" s="1">
-        <v>191321</v>
-      </c>
-      <c r="N11" s="1">
-        <v>192522</v>
-      </c>
-      <c r="O11" s="1">
-        <v>194925</v>
-      </c>
-      <c r="P11" s="1">
-        <v>196126</v>
-      </c>
-      <c r="Q11" s="1">
-        <v>197327</v>
-      </c>
-      <c r="R11" s="1">
-        <v>199730</v>
-      </c>
-      <c r="S11" s="1">
-        <v>195838</v>
-      </c>
-      <c r="T11" s="1">
-        <v>201027</v>
-      </c>
-      <c r="U11" s="1">
-        <v>202324</v>
-      </c>
-      <c r="V11" s="1">
-        <v>202324</v>
-      </c>
-      <c r="W11" s="1">
-        <v>203621</v>
-      </c>
-      <c r="X11" s="1">
-        <v>202324</v>
-      </c>
-      <c r="Y11" s="1">
-        <v>201027</v>
-      </c>
-      <c r="Z11" s="1">
-        <v>202324</v>
-      </c>
-      <c r="AA11" s="1">
-        <v>204919</v>
-      </c>
-      <c r="AB11" s="1">
-        <v>206216</v>
-      </c>
-      <c r="AC11" s="1">
-        <v>207513</v>
-      </c>
-      <c r="AD11" s="1">
-        <v>209339</v>
-      </c>
-      <c r="AE11" s="1">
-        <v>205159</v>
-      </c>
-      <c r="AF11" s="1">
-        <v>210732</v>
-      </c>
-      <c r="AG11" s="1">
-        <v>212126</v>
-      </c>
-      <c r="AH11" s="1">
-        <v>212126</v>
-      </c>
-      <c r="AI11" s="1">
-        <v>213519</v>
-      </c>
-      <c r="AJ11" s="1">
-        <v>212126</v>
-      </c>
-      <c r="AK11" s="1">
-        <v>210732</v>
-      </c>
-      <c r="AL11" s="1">
-        <v>212126</v>
-      </c>
-      <c r="AM11" s="1">
-        <v>214913</v>
-      </c>
-      <c r="AN11" s="1">
-        <v>216306</v>
-      </c>
-      <c r="AO11" s="1">
-        <v>217700</v>
+        <v>LIABILITIES</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+      <c r="Q11" t="str">
+        <v/>
+      </c>
+      <c r="R11" t="str">
+        <v/>
+      </c>
+      <c r="S11" t="str">
+        <v/>
+      </c>
+      <c r="T11" t="str">
+        <v/>
+      </c>
+      <c r="U11" t="str">
+        <v/>
+      </c>
+      <c r="V11" t="str">
+        <v/>
+      </c>
+      <c r="W11" t="str">
+        <v/>
+      </c>
+      <c r="X11" t="str">
+        <v/>
+      </c>
+      <c r="Y11" t="str">
+        <v/>
+      </c>
+      <c r="Z11" t="str">
+        <v/>
+      </c>
+      <c r="AA11" t="str">
+        <v/>
+      </c>
+      <c r="AB11" t="str">
+        <v/>
+      </c>
+      <c r="AC11" t="str">
+        <v/>
+      </c>
+      <c r="AD11" t="str">
+        <v/>
+      </c>
+      <c r="AE11" t="str">
+        <v/>
+      </c>
+      <c r="AF11" t="str">
+        <v/>
+      </c>
+      <c r="AG11" t="str">
+        <v/>
+      </c>
+      <c r="AH11" t="str">
+        <v/>
+      </c>
+      <c r="AI11" t="str">
+        <v/>
+      </c>
+      <c r="AJ11" t="str">
+        <v/>
+      </c>
+      <c r="AK11" t="str">
+        <v/>
+      </c>
+      <c r="AL11" t="str">
+        <v/>
+      </c>
+      <c r="AM11" t="str">
+        <v/>
+      </c>
+      <c r="AN11" t="str">
+        <v/>
+      </c>
+      <c r="AO11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v xml:space="preserve">  Other Current Liabilities</v>
+        <v xml:space="preserve">  Current Liabilities</v>
       </c>
       <c r="B12" s="1">
-        <v>70000</v>
+        <v>197327</v>
       </c>
       <c r="C12" s="1">
-        <v>70000</v>
+        <v>207513</v>
       </c>
       <c r="D12" s="1">
-        <v>70000</v>
+        <v>217700</v>
       </c>
       <c r="E12" s="1">
-        <v>70000</v>
+        <v>217700</v>
       </c>
       <c r="F12" s="1">
-        <v>70000</v>
+        <v>190120</v>
       </c>
       <c r="G12" s="1">
-        <v>70000</v>
+        <v>186516</v>
       </c>
       <c r="H12" s="1">
-        <v>70000</v>
+        <v>191321</v>
       </c>
       <c r="I12" s="1">
-        <v>70000</v>
+        <v>192522</v>
       </c>
       <c r="J12" s="1">
-        <v>70000</v>
+        <v>192522</v>
       </c>
       <c r="K12" s="1">
-        <v>70000</v>
+        <v>193724</v>
       </c>
       <c r="L12" s="1">
-        <v>70000</v>
+        <v>192522</v>
       </c>
       <c r="M12" s="1">
-        <v>70000</v>
+        <v>191321</v>
       </c>
       <c r="N12" s="1">
-        <v>70000</v>
+        <v>192522</v>
       </c>
       <c r="O12" s="1">
-        <v>70000</v>
+        <v>194925</v>
       </c>
       <c r="P12" s="1">
-        <v>70000</v>
+        <v>196126</v>
       </c>
       <c r="Q12" s="1">
-        <v>70000</v>
+        <v>197327</v>
       </c>
       <c r="R12" s="1">
-        <v>70000</v>
+        <v>199730</v>
       </c>
       <c r="S12" s="1">
-        <v>70000</v>
+        <v>195838</v>
       </c>
       <c r="T12" s="1">
-        <v>70000</v>
+        <v>201027</v>
       </c>
       <c r="U12" s="1">
-        <v>70000</v>
+        <v>202324</v>
       </c>
       <c r="V12" s="1">
-        <v>70000</v>
+        <v>202324</v>
       </c>
       <c r="W12" s="1">
-        <v>70000</v>
+        <v>203621</v>
       </c>
       <c r="X12" s="1">
-        <v>70000</v>
+        <v>202324</v>
       </c>
       <c r="Y12" s="1">
-        <v>70000</v>
+        <v>201027</v>
       </c>
       <c r="Z12" s="1">
-        <v>70000</v>
+        <v>202324</v>
       </c>
       <c r="AA12" s="1">
-        <v>70000</v>
+        <v>204919</v>
       </c>
       <c r="AB12" s="1">
-        <v>70000</v>
+        <v>206216</v>
       </c>
       <c r="AC12" s="1">
-        <v>70000</v>
+        <v>207513</v>
       </c>
       <c r="AD12" s="1">
-        <v>70000</v>
+        <v>209339</v>
       </c>
       <c r="AE12" s="1">
-        <v>70000</v>
+        <v>205159</v>
       </c>
       <c r="AF12" s="1">
-        <v>70000</v>
+        <v>210732</v>
       </c>
       <c r="AG12" s="1">
-        <v>70000</v>
+        <v>212126</v>
       </c>
       <c r="AH12" s="1">
-        <v>70000</v>
+        <v>212126</v>
       </c>
       <c r="AI12" s="1">
-        <v>70000</v>
+        <v>213519</v>
       </c>
       <c r="AJ12" s="1">
-        <v>70000</v>
+        <v>212126</v>
       </c>
       <c r="AK12" s="1">
-        <v>70000</v>
+        <v>210732</v>
       </c>
       <c r="AL12" s="1">
-        <v>70000</v>
+        <v>212126</v>
       </c>
       <c r="AM12" s="1">
-        <v>70000</v>
+        <v>214913</v>
       </c>
       <c r="AN12" s="1">
-        <v>70000</v>
+        <v>216306</v>
       </c>
       <c r="AO12" s="1">
-        <v>70000</v>
+        <v>217700</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Total Current Liabilities</v>
+        <v xml:space="preserve">  Other Current Liabilities</v>
       </c>
       <c r="B13" s="1">
-        <v>267327</v>
+        <v>70000</v>
       </c>
       <c r="C13" s="1">
-        <v>277513</v>
+        <v>70000</v>
       </c>
       <c r="D13" s="1">
-        <v>287700</v>
+        <v>70000</v>
       </c>
       <c r="E13" s="1">
-        <v>287700</v>
+        <v>70000</v>
       </c>
       <c r="F13" s="1">
-        <v>260120</v>
+        <v>70000</v>
       </c>
       <c r="G13" s="1">
-        <v>256516</v>
+        <v>70000</v>
       </c>
       <c r="H13" s="1">
-        <v>261321</v>
+        <v>70000</v>
       </c>
       <c r="I13" s="1">
-        <v>262522</v>
+        <v>70000</v>
       </c>
       <c r="J13" s="1">
-        <v>262522</v>
+        <v>70000</v>
       </c>
       <c r="K13" s="1">
-        <v>263724</v>
+        <v>70000</v>
       </c>
       <c r="L13" s="1">
-        <v>262522</v>
+        <v>70000</v>
       </c>
       <c r="M13" s="1">
-        <v>261321</v>
+        <v>70000</v>
       </c>
       <c r="N13" s="1">
-        <v>262522</v>
+        <v>70000</v>
       </c>
       <c r="O13" s="1">
-        <v>264925</v>
+        <v>70000</v>
       </c>
       <c r="P13" s="1">
-        <v>266126</v>
+        <v>70000</v>
       </c>
       <c r="Q13" s="1">
-        <v>267327</v>
+        <v>70000</v>
       </c>
       <c r="R13" s="1">
-        <v>269730</v>
+        <v>70000</v>
       </c>
       <c r="S13" s="1">
-        <v>265838</v>
+        <v>70000</v>
       </c>
       <c r="T13" s="1">
-        <v>271027</v>
+        <v>70000</v>
       </c>
       <c r="U13" s="1">
-        <v>272324</v>
+        <v>70000</v>
       </c>
       <c r="V13" s="1">
-        <v>272324</v>
+        <v>70000</v>
       </c>
       <c r="W13" s="1">
-        <v>273621</v>
+        <v>70000</v>
       </c>
       <c r="X13" s="1">
-        <v>272324</v>
+        <v>70000</v>
       </c>
       <c r="Y13" s="1">
-        <v>271027</v>
+        <v>70000</v>
       </c>
       <c r="Z13" s="1">
-        <v>272324</v>
+        <v>70000</v>
       </c>
       <c r="AA13" s="1">
-        <v>274919</v>
+        <v>70000</v>
       </c>
       <c r="AB13" s="1">
-        <v>276216</v>
+        <v>70000</v>
       </c>
       <c r="AC13" s="1">
-        <v>277513</v>
+        <v>70000</v>
       </c>
       <c r="AD13" s="1">
-        <v>279339</v>
+        <v>70000</v>
       </c>
       <c r="AE13" s="1">
-        <v>275159</v>
+        <v>70000</v>
       </c>
       <c r="AF13" s="1">
-        <v>280732</v>
+        <v>70000</v>
       </c>
       <c r="AG13" s="1">
-        <v>282126</v>
+        <v>70000</v>
       </c>
       <c r="AH13" s="1">
-        <v>282126</v>
+        <v>70000</v>
       </c>
       <c r="AI13" s="1">
-        <v>283519</v>
+        <v>70000</v>
       </c>
       <c r="AJ13" s="1">
-        <v>282126</v>
+        <v>70000</v>
       </c>
       <c r="AK13" s="1">
-        <v>280732</v>
+        <v>70000</v>
       </c>
       <c r="AL13" s="1">
-        <v>282126</v>
+        <v>70000</v>
       </c>
       <c r="AM13" s="1">
-        <v>284913</v>
+        <v>70000</v>
       </c>
       <c r="AN13" s="1">
-        <v>286306</v>
+        <v>70000</v>
       </c>
       <c r="AO13" s="1">
-        <v>287700</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v xml:space="preserve">  Long Term Liabilities</v>
+        <v>Total Current Liabilities</v>
       </c>
       <c r="B14" s="1">
-        <v>690000</v>
+        <v>267327</v>
       </c>
       <c r="C14" s="1">
-        <v>570000</v>
+        <v>277513</v>
       </c>
       <c r="D14" s="1">
-        <v>450000</v>
+        <v>287700</v>
       </c>
       <c r="E14" s="1">
-        <v>450000</v>
+        <v>287700</v>
       </c>
       <c r="F14" s="1">
-        <v>800000</v>
+        <v>260120</v>
       </c>
       <c r="G14" s="1">
-        <v>790000</v>
+        <v>256516</v>
       </c>
       <c r="H14" s="1">
-        <v>780000</v>
+        <v>261321</v>
       </c>
       <c r="I14" s="1">
-        <v>770000</v>
+        <v>262522</v>
       </c>
       <c r="J14" s="1">
-        <v>760000</v>
+        <v>262522</v>
       </c>
       <c r="K14" s="1">
-        <v>750000</v>
+        <v>263724</v>
       </c>
       <c r="L14" s="1">
-        <v>740000</v>
+        <v>262522</v>
       </c>
       <c r="M14" s="1">
-        <v>730000</v>
+        <v>261321</v>
       </c>
       <c r="N14" s="1">
-        <v>720000</v>
+        <v>262522</v>
       </c>
       <c r="O14" s="1">
-        <v>710000</v>
+        <v>264925</v>
       </c>
       <c r="P14" s="1">
-        <v>700000</v>
+        <v>266126</v>
       </c>
       <c r="Q14" s="1">
-        <v>690000</v>
+        <v>267327</v>
       </c>
       <c r="R14" s="1">
-        <v>680000</v>
+        <v>269730</v>
       </c>
       <c r="S14" s="1">
-        <v>670000</v>
+        <v>265838</v>
       </c>
       <c r="T14" s="1">
-        <v>660000</v>
+        <v>271027</v>
       </c>
       <c r="U14" s="1">
-        <v>650000</v>
+        <v>272324</v>
       </c>
       <c r="V14" s="1">
-        <v>640000</v>
+        <v>272324</v>
       </c>
       <c r="W14" s="1">
-        <v>630000</v>
+        <v>273621</v>
       </c>
       <c r="X14" s="1">
-        <v>620000</v>
+        <v>272324</v>
       </c>
       <c r="Y14" s="1">
-        <v>610000</v>
+        <v>271027</v>
       </c>
       <c r="Z14" s="1">
-        <v>600000</v>
+        <v>272324</v>
       </c>
       <c r="AA14" s="1">
-        <v>590000</v>
+        <v>274919</v>
       </c>
       <c r="AB14" s="1">
-        <v>580000</v>
+        <v>276216</v>
       </c>
       <c r="AC14" s="1">
-        <v>570000</v>
+        <v>277513</v>
       </c>
       <c r="AD14" s="1">
-        <v>560000</v>
+        <v>279339</v>
       </c>
       <c r="AE14" s="1">
-        <v>550000</v>
+        <v>275159</v>
       </c>
       <c r="AF14" s="1">
-        <v>540000</v>
+        <v>280732</v>
       </c>
       <c r="AG14" s="1">
-        <v>530000</v>
+        <v>282126</v>
       </c>
       <c r="AH14" s="1">
-        <v>520000</v>
+        <v>282126</v>
       </c>
       <c r="AI14" s="1">
-        <v>510000</v>
+        <v>283519</v>
       </c>
       <c r="AJ14" s="1">
-        <v>500000</v>
+        <v>282126</v>
       </c>
       <c r="AK14" s="1">
-        <v>490000</v>
+        <v>280732</v>
       </c>
       <c r="AL14" s="1">
-        <v>480000</v>
+        <v>282126</v>
       </c>
       <c r="AM14" s="1">
-        <v>470000</v>
+        <v>284913</v>
       </c>
       <c r="AN14" s="1">
-        <v>460000</v>
+        <v>286306</v>
       </c>
       <c r="AO14" s="1">
-        <v>450000</v>
+        <v>287700</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Total Liabilities</v>
+        <v xml:space="preserve">  Long Term Liabilities</v>
       </c>
       <c r="B15" s="1">
-        <v>957327</v>
+        <v>690000</v>
       </c>
       <c r="C15" s="1">
-        <v>847513</v>
+        <v>570000</v>
       </c>
       <c r="D15" s="1">
-        <v>737700</v>
+        <v>450000</v>
       </c>
       <c r="E15" s="1">
-        <v>737700</v>
+        <v>450000</v>
       </c>
       <c r="F15" s="1">
-        <v>1060120</v>
+        <v>800000</v>
       </c>
       <c r="G15" s="1">
-        <v>1046516</v>
+        <v>790000</v>
       </c>
       <c r="H15" s="1">
-        <v>1041321</v>
+        <v>780000</v>
       </c>
       <c r="I15" s="1">
-        <v>1032522</v>
+        <v>770000</v>
       </c>
       <c r="J15" s="1">
-        <v>1022522</v>
+        <v>760000</v>
       </c>
       <c r="K15" s="1">
-        <v>1013724</v>
+        <v>750000</v>
       </c>
       <c r="L15" s="1">
-        <v>1002522</v>
+        <v>740000</v>
       </c>
       <c r="M15" s="1">
-        <v>991321</v>
+        <v>730000</v>
       </c>
       <c r="N15" s="1">
-        <v>982522</v>
+        <v>720000</v>
       </c>
       <c r="O15" s="1">
-        <v>974925</v>
+        <v>710000</v>
       </c>
       <c r="P15" s="1">
-        <v>966126</v>
+        <v>700000</v>
       </c>
       <c r="Q15" s="1">
-        <v>957327</v>
+        <v>690000</v>
       </c>
       <c r="R15" s="1">
-        <v>949730</v>
+        <v>680000</v>
       </c>
       <c r="S15" s="1">
-        <v>935838</v>
+        <v>670000</v>
       </c>
       <c r="T15" s="1">
-        <v>931027</v>
+        <v>660000</v>
       </c>
       <c r="U15" s="1">
-        <v>922324</v>
+        <v>650000</v>
       </c>
       <c r="V15" s="1">
-        <v>912324</v>
+        <v>640000</v>
       </c>
       <c r="W15" s="1">
-        <v>903621</v>
+        <v>630000</v>
       </c>
       <c r="X15" s="1">
-        <v>892324</v>
+        <v>620000</v>
       </c>
       <c r="Y15" s="1">
-        <v>881027</v>
+        <v>610000</v>
       </c>
       <c r="Z15" s="1">
-        <v>872324</v>
+        <v>600000</v>
       </c>
       <c r="AA15" s="1">
-        <v>864919</v>
+        <v>590000</v>
       </c>
       <c r="AB15" s="1">
-        <v>856216</v>
+        <v>580000</v>
       </c>
       <c r="AC15" s="1">
-        <v>847513</v>
+        <v>570000</v>
       </c>
       <c r="AD15" s="1">
-        <v>839339</v>
+        <v>560000</v>
       </c>
       <c r="AE15" s="1">
-        <v>825159</v>
+        <v>550000</v>
       </c>
       <c r="AF15" s="1">
-        <v>820732</v>
+        <v>540000</v>
       </c>
       <c r="AG15" s="1">
-        <v>812126</v>
+        <v>530000</v>
       </c>
       <c r="AH15" s="1">
-        <v>802126</v>
+        <v>520000</v>
       </c>
       <c r="AI15" s="1">
-        <v>793519</v>
+        <v>510000</v>
       </c>
       <c r="AJ15" s="1">
-        <v>782126</v>
+        <v>500000</v>
       </c>
       <c r="AK15" s="1">
-        <v>770732</v>
+        <v>490000</v>
       </c>
       <c r="AL15" s="1">
-        <v>762126</v>
+        <v>480000</v>
       </c>
       <c r="AM15" s="1">
-        <v>754913</v>
+        <v>470000</v>
       </c>
       <c r="AN15" s="1">
-        <v>746306</v>
+        <v>460000</v>
       </c>
       <c r="AO15" s="1">
-        <v>737700</v>
+        <v>450000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>EQUITY</v>
-      </c>
-      <c r="B16" t="str">
-        <v/>
-      </c>
-      <c r="C16" t="str">
-        <v/>
-      </c>
-      <c r="D16" t="str">
-        <v/>
-      </c>
-      <c r="E16" t="str">
-        <v/>
-      </c>
-      <c r="F16" t="str">
-        <v/>
-      </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
-        <v/>
-      </c>
-      <c r="I16" t="str">
-        <v/>
-      </c>
-      <c r="J16" t="str">
-        <v/>
-      </c>
-      <c r="K16" t="str">
-        <v/>
-      </c>
-      <c r="L16" t="str">
-        <v/>
-      </c>
-      <c r="M16" t="str">
-        <v/>
-      </c>
-      <c r="N16" t="str">
-        <v/>
-      </c>
-      <c r="O16" t="str">
-        <v/>
-      </c>
-      <c r="P16" t="str">
-        <v/>
-      </c>
-      <c r="Q16" t="str">
-        <v/>
-      </c>
-      <c r="R16" t="str">
-        <v/>
-      </c>
-      <c r="S16" t="str">
-        <v/>
-      </c>
-      <c r="T16" t="str">
-        <v/>
-      </c>
-      <c r="U16" t="str">
-        <v/>
-      </c>
-      <c r="V16" t="str">
-        <v/>
-      </c>
-      <c r="W16" t="str">
-        <v/>
-      </c>
-      <c r="X16" t="str">
-        <v/>
-      </c>
-      <c r="Y16" t="str">
-        <v/>
-      </c>
-      <c r="Z16" t="str">
-        <v/>
-      </c>
-      <c r="AA16" t="str">
-        <v/>
-      </c>
-      <c r="AB16" t="str">
-        <v/>
-      </c>
-      <c r="AC16" t="str">
-        <v/>
-      </c>
-      <c r="AD16" t="str">
-        <v/>
-      </c>
-      <c r="AE16" t="str">
-        <v/>
-      </c>
-      <c r="AF16" t="str">
-        <v/>
-      </c>
-      <c r="AG16" t="str">
-        <v/>
-      </c>
-      <c r="AH16" t="str">
-        <v/>
-      </c>
-      <c r="AI16" t="str">
-        <v/>
-      </c>
-      <c r="AJ16" t="str">
-        <v/>
-      </c>
-      <c r="AK16" t="str">
-        <v/>
-      </c>
-      <c r="AL16" t="str">
-        <v/>
-      </c>
-      <c r="AM16" t="str">
-        <v/>
-      </c>
-      <c r="AN16" t="str">
-        <v/>
-      </c>
-      <c r="AO16" t="str">
-        <v/>
+        <v>Total Non-Current Liabilities</v>
+      </c>
+      <c r="B16" s="1">
+        <v>690000</v>
+      </c>
+      <c r="C16" s="1">
+        <v>570000</v>
+      </c>
+      <c r="D16" s="1">
+        <v>450000</v>
+      </c>
+      <c r="E16" s="1">
+        <v>450000</v>
+      </c>
+      <c r="F16" s="1">
+        <v>800000</v>
+      </c>
+      <c r="G16" s="1">
+        <v>790000</v>
+      </c>
+      <c r="H16" s="1">
+        <v>780000</v>
+      </c>
+      <c r="I16" s="1">
+        <v>770000</v>
+      </c>
+      <c r="J16" s="1">
+        <v>760000</v>
+      </c>
+      <c r="K16" s="1">
+        <v>750000</v>
+      </c>
+      <c r="L16" s="1">
+        <v>740000</v>
+      </c>
+      <c r="M16" s="1">
+        <v>730000</v>
+      </c>
+      <c r="N16" s="1">
+        <v>720000</v>
+      </c>
+      <c r="O16" s="1">
+        <v>710000</v>
+      </c>
+      <c r="P16" s="1">
+        <v>700000</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>690000</v>
+      </c>
+      <c r="R16" s="1">
+        <v>680000</v>
+      </c>
+      <c r="S16" s="1">
+        <v>670000</v>
+      </c>
+      <c r="T16" s="1">
+        <v>660000</v>
+      </c>
+      <c r="U16" s="1">
+        <v>650000</v>
+      </c>
+      <c r="V16" s="1">
+        <v>640000</v>
+      </c>
+      <c r="W16" s="1">
+        <v>630000</v>
+      </c>
+      <c r="X16" s="1">
+        <v>620000</v>
+      </c>
+      <c r="Y16" s="1">
+        <v>610000</v>
+      </c>
+      <c r="Z16" s="1">
+        <v>600000</v>
+      </c>
+      <c r="AA16" s="1">
+        <v>590000</v>
+      </c>
+      <c r="AB16" s="1">
+        <v>580000</v>
+      </c>
+      <c r="AC16" s="1">
+        <v>570000</v>
+      </c>
+      <c r="AD16" s="1">
+        <v>560000</v>
+      </c>
+      <c r="AE16" s="1">
+        <v>550000</v>
+      </c>
+      <c r="AF16" s="1">
+        <v>540000</v>
+      </c>
+      <c r="AG16" s="1">
+        <v>530000</v>
+      </c>
+      <c r="AH16" s="1">
+        <v>520000</v>
+      </c>
+      <c r="AI16" s="1">
+        <v>510000</v>
+      </c>
+      <c r="AJ16" s="1">
+        <v>500000</v>
+      </c>
+      <c r="AK16" s="1">
+        <v>490000</v>
+      </c>
+      <c r="AL16" s="1">
+        <v>480000</v>
+      </c>
+      <c r="AM16" s="1">
+        <v>470000</v>
+      </c>
+      <c r="AN16" s="1">
+        <v>460000</v>
+      </c>
+      <c r="AO16" s="1">
+        <v>450000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v xml:space="preserve">  Total Equity</v>
+        <v>Total Liabilities</v>
       </c>
       <c r="B17" s="1">
-        <v>1984548</v>
+        <v>957327</v>
       </c>
       <c r="C17" s="1">
-        <v>3419980</v>
+        <v>847513</v>
       </c>
       <c r="D17" s="1">
-        <v>5028526</v>
+        <v>737700</v>
       </c>
       <c r="E17" s="1">
-        <v>5028526</v>
+        <v>737700</v>
       </c>
       <c r="F17" s="1">
-        <v>841780</v>
+        <v>1060120</v>
       </c>
       <c r="G17" s="1">
-        <v>917651</v>
+        <v>1046516</v>
       </c>
       <c r="H17" s="1">
-        <v>1036857</v>
+        <v>1041321</v>
       </c>
       <c r="I17" s="1">
-        <v>1142678</v>
+        <v>1032522</v>
       </c>
       <c r="J17" s="1">
-        <v>1243400</v>
+        <v>1022522</v>
       </c>
       <c r="K17" s="1">
-        <v>1350631</v>
+        <v>1013724</v>
       </c>
       <c r="L17" s="1">
-        <v>1445755</v>
+        <v>1002522</v>
       </c>
       <c r="M17" s="1">
-        <v>1538967</v>
+        <v>991321</v>
       </c>
       <c r="N17" s="1">
-        <v>1644788</v>
+        <v>982522</v>
       </c>
       <c r="O17" s="1">
-        <v>1759529</v>
+        <v>974925</v>
       </c>
       <c r="P17" s="1">
-        <v>1871083</v>
+        <v>966126</v>
       </c>
       <c r="Q17" s="1">
-        <v>1984548</v>
+        <v>957327</v>
       </c>
       <c r="R17" s="1">
-        <v>2115753</v>
+        <v>949730</v>
       </c>
       <c r="S17" s="1">
-        <v>2204049</v>
+        <v>935838</v>
       </c>
       <c r="T17" s="1">
-        <v>2339148</v>
+        <v>931027</v>
       </c>
       <c r="U17" s="1">
-        <v>2459791</v>
+        <v>922324</v>
       </c>
       <c r="V17" s="1">
-        <v>2574927</v>
+        <v>912324</v>
       </c>
       <c r="W17" s="1">
-        <v>2697134</v>
+        <v>903621</v>
       </c>
       <c r="X17" s="1">
-        <v>2806263</v>
+        <v>892324</v>
       </c>
       <c r="Y17" s="1">
-        <v>2913328</v>
+        <v>881027</v>
       </c>
       <c r="Z17" s="1">
-        <v>3033971</v>
+        <v>872324</v>
       </c>
       <c r="AA17" s="1">
-        <v>3164247</v>
+        <v>864919</v>
       </c>
       <c r="AB17" s="1">
-        <v>3291081</v>
+        <v>856216</v>
       </c>
       <c r="AC17" s="1">
-        <v>3419980</v>
+        <v>847513</v>
       </c>
       <c r="AD17" s="1">
-        <v>3562846</v>
+        <v>839339</v>
       </c>
       <c r="AE17" s="1">
-        <v>3663567</v>
+        <v>825159</v>
       </c>
       <c r="AF17" s="1">
-        <v>3814559</v>
+        <v>820732</v>
       </c>
       <c r="AG17" s="1">
-        <v>3950022</v>
+        <v>812126</v>
       </c>
       <c r="AH17" s="1">
-        <v>4079571</v>
+        <v>802126</v>
       </c>
       <c r="AI17" s="1">
-        <v>4216753</v>
+        <v>793519</v>
       </c>
       <c r="AJ17" s="1">
-        <v>4339887</v>
+        <v>782126</v>
       </c>
       <c r="AK17" s="1">
-        <v>4460806</v>
+        <v>770732</v>
       </c>
       <c r="AL17" s="1">
-        <v>4596269</v>
+        <v>762126</v>
       </c>
       <c r="AM17" s="1">
-        <v>4742081</v>
+        <v>754913</v>
       </c>
       <c r="AN17" s="1">
-        <v>4884196</v>
+        <v>746306</v>
       </c>
       <c r="AO17" s="1">
-        <v>5028526</v>
+        <v>737700</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
+        <v>EQUITY</v>
+      </c>
+      <c r="B18" t="str">
+        <v/>
+      </c>
+      <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
+        <v/>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+      <c r="Q18" t="str">
+        <v/>
+      </c>
+      <c r="R18" t="str">
+        <v/>
+      </c>
+      <c r="S18" t="str">
+        <v/>
+      </c>
+      <c r="T18" t="str">
+        <v/>
+      </c>
+      <c r="U18" t="str">
+        <v/>
+      </c>
+      <c r="V18" t="str">
+        <v/>
+      </c>
+      <c r="W18" t="str">
+        <v/>
+      </c>
+      <c r="X18" t="str">
+        <v/>
+      </c>
+      <c r="Y18" t="str">
+        <v/>
+      </c>
+      <c r="Z18" t="str">
+        <v/>
+      </c>
+      <c r="AA18" t="str">
+        <v/>
+      </c>
+      <c r="AB18" t="str">
+        <v/>
+      </c>
+      <c r="AC18" t="str">
+        <v/>
+      </c>
+      <c r="AD18" t="str">
+        <v/>
+      </c>
+      <c r="AE18" t="str">
+        <v/>
+      </c>
+      <c r="AF18" t="str">
+        <v/>
+      </c>
+      <c r="AG18" t="str">
+        <v/>
+      </c>
+      <c r="AH18" t="str">
+        <v/>
+      </c>
+      <c r="AI18" t="str">
+        <v/>
+      </c>
+      <c r="AJ18" t="str">
+        <v/>
+      </c>
+      <c r="AK18" t="str">
+        <v/>
+      </c>
+      <c r="AL18" t="str">
+        <v/>
+      </c>
+      <c r="AM18" t="str">
+        <v/>
+      </c>
+      <c r="AN18" t="str">
+        <v/>
+      </c>
+      <c r="AO18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v xml:space="preserve">  Total Equity</v>
+      </c>
+      <c r="B19" s="1">
+        <v>1948182</v>
+      </c>
+      <c r="C19" s="1">
+        <v>3368588</v>
+      </c>
+      <c r="D19" s="1">
+        <v>4962110</v>
+      </c>
+      <c r="E19" s="1">
+        <v>4962110</v>
+      </c>
+      <c r="F19" s="1">
+        <v>816880</v>
+      </c>
+      <c r="G19" s="1">
+        <v>898484</v>
+      </c>
+      <c r="H19" s="1">
+        <v>1010046</v>
+      </c>
+      <c r="I19" s="1">
+        <v>1113956</v>
+      </c>
+      <c r="J19" s="1">
+        <v>1214678</v>
+      </c>
+      <c r="K19" s="1">
+        <v>1320498</v>
+      </c>
+      <c r="L19" s="1">
+        <v>1417533</v>
+      </c>
+      <c r="M19" s="1">
+        <v>1512656</v>
+      </c>
+      <c r="N19" s="1">
+        <v>1616066</v>
+      </c>
+      <c r="O19" s="1">
+        <v>1726985</v>
+      </c>
+      <c r="P19" s="1">
+        <v>1836628</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>1948182</v>
+      </c>
+      <c r="R19" s="1">
+        <v>2076745</v>
+      </c>
+      <c r="S19" s="1">
+        <v>2171233</v>
+      </c>
+      <c r="T19" s="1">
+        <v>2298076</v>
+      </c>
+      <c r="U19" s="1">
+        <v>2416655</v>
+      </c>
+      <c r="V19" s="1">
+        <v>2531791</v>
+      </c>
+      <c r="W19" s="1">
+        <v>2652434</v>
+      </c>
+      <c r="X19" s="1">
+        <v>2763627</v>
+      </c>
+      <c r="Y19" s="1">
+        <v>2872756</v>
+      </c>
+      <c r="Z19" s="1">
+        <v>2990835</v>
+      </c>
+      <c r="AA19" s="1">
+        <v>3116984</v>
+      </c>
+      <c r="AB19" s="1">
+        <v>3241754</v>
+      </c>
+      <c r="AC19" s="1">
+        <v>3368588</v>
+      </c>
+      <c r="AD19" s="1">
+        <v>3509730</v>
+      </c>
+      <c r="AE19" s="1">
+        <v>3617102</v>
+      </c>
+      <c r="AF19" s="1">
+        <v>3759226</v>
+      </c>
+      <c r="AG19" s="1">
+        <v>3892473</v>
+      </c>
+      <c r="AH19" s="1">
+        <v>4022022</v>
+      </c>
+      <c r="AI19" s="1">
+        <v>4157486</v>
+      </c>
+      <c r="AJ19" s="1">
+        <v>4282838</v>
+      </c>
+      <c r="AK19" s="1">
+        <v>4405973</v>
+      </c>
+      <c r="AL19" s="1">
+        <v>4538720</v>
+      </c>
+      <c r="AM19" s="1">
+        <v>4680098</v>
+      </c>
+      <c r="AN19" s="1">
+        <v>4819996</v>
+      </c>
+      <c r="AO19" s="1">
+        <v>4962110</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
         <v>TOTAL LIABILITIES &amp; EQUITY</v>
       </c>
-      <c r="B18" s="1">
-        <v>2941875</v>
-      </c>
-      <c r="C18" s="1">
-        <v>4267493</v>
-      </c>
-      <c r="D18" s="1">
-        <v>5766226</v>
-      </c>
-      <c r="E18" s="1">
-        <v>5766226</v>
-      </c>
-      <c r="F18" s="1">
-        <v>1901900</v>
-      </c>
-      <c r="G18" s="1">
-        <v>1964167</v>
-      </c>
-      <c r="H18" s="1">
-        <v>2078178</v>
-      </c>
-      <c r="I18" s="1">
-        <v>2175200</v>
-      </c>
-      <c r="J18" s="1">
-        <v>2265922</v>
-      </c>
-      <c r="K18" s="1">
-        <v>2364355</v>
-      </c>
-      <c r="L18" s="1">
-        <v>2448277</v>
-      </c>
-      <c r="M18" s="1">
-        <v>2530288</v>
-      </c>
-      <c r="N18" s="1">
-        <v>2627310</v>
-      </c>
-      <c r="O18" s="1">
-        <v>2734454</v>
-      </c>
-      <c r="P18" s="1">
-        <v>2837209</v>
-      </c>
-      <c r="Q18" s="1">
-        <v>2941875</v>
-      </c>
-      <c r="R18" s="1">
-        <v>3065483</v>
-      </c>
-      <c r="S18" s="1">
-        <v>3139887</v>
-      </c>
-      <c r="T18" s="1">
-        <v>3270175</v>
-      </c>
-      <c r="U18" s="1">
-        <v>3382115</v>
-      </c>
-      <c r="V18" s="1">
-        <v>3487251</v>
-      </c>
-      <c r="W18" s="1">
-        <v>3600755</v>
-      </c>
-      <c r="X18" s="1">
-        <v>3698587</v>
-      </c>
-      <c r="Y18" s="1">
-        <v>3794355</v>
-      </c>
-      <c r="Z18" s="1">
-        <v>3906295</v>
-      </c>
-      <c r="AA18" s="1">
-        <v>4029166</v>
-      </c>
-      <c r="AB18" s="1">
-        <v>4147297</v>
-      </c>
-      <c r="AC18" s="1">
-        <v>4267493</v>
-      </c>
-      <c r="AD18" s="1">
-        <v>4402185</v>
-      </c>
-      <c r="AE18" s="1">
-        <v>4488726</v>
-      </c>
-      <c r="AF18" s="1">
-        <v>4635291</v>
-      </c>
-      <c r="AG18" s="1">
-        <v>4762148</v>
-      </c>
-      <c r="AH18" s="1">
-        <v>4881697</v>
-      </c>
-      <c r="AI18" s="1">
-        <v>5010272</v>
-      </c>
-      <c r="AJ18" s="1">
-        <v>5122013</v>
-      </c>
-      <c r="AK18" s="1">
-        <v>5231538</v>
-      </c>
-      <c r="AL18" s="1">
-        <v>5358395</v>
-      </c>
-      <c r="AM18" s="1">
-        <v>5496994</v>
-      </c>
-      <c r="AN18" s="1">
-        <v>5630502</v>
-      </c>
-      <c r="AO18" s="1">
-        <v>5766226</v>
+      <c r="B20" s="1">
+        <v>2905509</v>
+      </c>
+      <c r="C20" s="1">
+        <v>4216101</v>
+      </c>
+      <c r="D20" s="1">
+        <v>5699810</v>
+      </c>
+      <c r="E20" s="1">
+        <v>5699810</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1877000</v>
+      </c>
+      <c r="G20" s="1">
+        <v>1945000</v>
+      </c>
+      <c r="H20" s="1">
+        <v>2051367</v>
+      </c>
+      <c r="I20" s="1">
+        <v>2146478</v>
+      </c>
+      <c r="J20" s="1">
+        <v>2237200</v>
+      </c>
+      <c r="K20" s="1">
+        <v>2334222</v>
+      </c>
+      <c r="L20" s="1">
+        <v>2420055</v>
+      </c>
+      <c r="M20" s="1">
+        <v>2503977</v>
+      </c>
+      <c r="N20" s="1">
+        <v>2598588</v>
+      </c>
+      <c r="O20" s="1">
+        <v>2701910</v>
+      </c>
+      <c r="P20" s="1">
+        <v>2802754</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>2905509</v>
+      </c>
+      <c r="R20" s="1">
+        <v>3026475</v>
+      </c>
+      <c r="S20" s="1">
+        <v>3107071</v>
+      </c>
+      <c r="T20" s="1">
+        <v>3229103</v>
+      </c>
+      <c r="U20" s="1">
+        <v>3338979</v>
+      </c>
+      <c r="V20" s="1">
+        <v>3444115</v>
+      </c>
+      <c r="W20" s="1">
+        <v>3556055</v>
+      </c>
+      <c r="X20" s="1">
+        <v>3655951</v>
+      </c>
+      <c r="Y20" s="1">
+        <v>3753783</v>
+      </c>
+      <c r="Z20" s="1">
+        <v>3863159</v>
+      </c>
+      <c r="AA20" s="1">
+        <v>3981903</v>
+      </c>
+      <c r="AB20" s="1">
+        <v>4097970</v>
+      </c>
+      <c r="AC20" s="1">
+        <v>4216101</v>
+      </c>
+      <c r="AD20" s="1">
+        <v>4349069</v>
+      </c>
+      <c r="AE20" s="1">
+        <v>4442261</v>
+      </c>
+      <c r="AF20" s="1">
+        <v>4579958</v>
+      </c>
+      <c r="AG20" s="1">
+        <v>4704599</v>
+      </c>
+      <c r="AH20" s="1">
+        <v>4824148</v>
+      </c>
+      <c r="AI20" s="1">
+        <v>4951005</v>
+      </c>
+      <c r="AJ20" s="1">
+        <v>5064964</v>
+      </c>
+      <c r="AK20" s="1">
+        <v>5176705</v>
+      </c>
+      <c r="AL20" s="1">
+        <v>5300846</v>
+      </c>
+      <c r="AM20" s="1">
+        <v>5435011</v>
+      </c>
+      <c r="AN20" s="1">
+        <v>5566302</v>
+      </c>
+      <c r="AO20" s="1">
+        <v>5699810</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Balance Check (Assets − L&amp;E)</v>
+      </c>
+      <c r="B21" s="1">
+        <v>36366</v>
+      </c>
+      <c r="C21" s="1">
+        <v>51392</v>
+      </c>
+      <c r="D21" s="1">
+        <v>66416</v>
+      </c>
+      <c r="E21" s="1">
+        <v>66416</v>
+      </c>
+      <c r="F21" s="1">
+        <v>24900</v>
+      </c>
+      <c r="G21" s="1">
+        <v>19167</v>
+      </c>
+      <c r="H21" s="1">
+        <v>26811</v>
+      </c>
+      <c r="I21" s="1">
+        <v>28722</v>
+      </c>
+      <c r="J21" s="1">
+        <v>28722</v>
+      </c>
+      <c r="K21" s="1">
+        <v>30133</v>
+      </c>
+      <c r="L21" s="1">
+        <v>28222</v>
+      </c>
+      <c r="M21" s="1">
+        <v>26311</v>
+      </c>
+      <c r="N21" s="1">
+        <v>28722</v>
+      </c>
+      <c r="O21" s="1">
+        <v>32544</v>
+      </c>
+      <c r="P21" s="1">
+        <v>34455</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>36366</v>
+      </c>
+      <c r="R21" s="1">
+        <v>39008</v>
+      </c>
+      <c r="S21" s="1">
+        <v>32816</v>
+      </c>
+      <c r="T21" s="1">
+        <v>41072</v>
+      </c>
+      <c r="U21" s="1">
+        <v>43136</v>
+      </c>
+      <c r="V21" s="1">
+        <v>43136</v>
+      </c>
+      <c r="W21" s="1">
+        <v>44700</v>
+      </c>
+      <c r="X21" s="1">
+        <v>42636</v>
+      </c>
+      <c r="Y21" s="1">
+        <v>40572</v>
+      </c>
+      <c r="Z21" s="1">
+        <v>43136</v>
+      </c>
+      <c r="AA21" s="1">
+        <v>47263</v>
+      </c>
+      <c r="AB21" s="1">
+        <v>49327</v>
+      </c>
+      <c r="AC21" s="1">
+        <v>51392</v>
+      </c>
+      <c r="AD21" s="1">
+        <v>53116</v>
+      </c>
+      <c r="AE21" s="1">
+        <v>46465</v>
+      </c>
+      <c r="AF21" s="1">
+        <v>55333</v>
+      </c>
+      <c r="AG21" s="1">
+        <v>57549</v>
+      </c>
+      <c r="AH21" s="1">
+        <v>57549</v>
+      </c>
+      <c r="AI21" s="1">
+        <v>59267</v>
+      </c>
+      <c r="AJ21" s="1">
+        <v>57049</v>
+      </c>
+      <c r="AK21" s="1">
+        <v>54833</v>
+      </c>
+      <c r="AL21" s="1">
+        <v>57549</v>
+      </c>
+      <c r="AM21" s="1">
+        <v>61983</v>
+      </c>
+      <c r="AN21" s="1">
+        <v>64200</v>
+      </c>
+      <c r="AO21" s="1">
+        <v>66416</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AO18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AO21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -36782,7 +36907,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Change in NWC</v>
+        <v>Change in NWC (Operating)</v>
       </c>
       <c r="B3" s="1">
         <v>-30593</v>
